--- a/results/link-prediction-gcn/Link/1shot/CiteSeer/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/CiteSeer/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.5311±0.0440</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.4861±0.0054</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.4777±0.0161</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4703±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5872±0.0326</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5872±0.0326</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5872±0.0326</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.5249±0.0352</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5733±0.0175</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5678±0.0400</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5311±0.0440</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4780±0.0059</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5106±0.0407</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5923±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5923±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5923±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.5484±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.6484±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.5799±0.0805</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5527±0.0738</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5527±0.0738</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5527±0.0738</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.6004±0.0242</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.5799±0.0539</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5220±0.0155</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4890±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4934±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4568±0.0069</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4989±0.0162</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.4978±0.0031</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.6106±0.0510</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.6106±0.0510</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.6106±0.0510</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.5022±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.5022±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.5022±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5637±0.0264</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.6322±0.0270</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.5132±0.0103</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.5978±0.0164</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4802±0.0087</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5062±0.0418</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.5018±0.0026</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.6670±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6546±0.0325</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6549±0.0225</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6549±0.0225</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6549±0.0225</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6681±0.0257</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6817±0.0070</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6663±0.0234</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.5198±0.0188</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4678±0.0241</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.4784±0.0175</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4374±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.5011±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5608±0.0509</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5608±0.0509</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5608±0.0509</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.4982±0.0019</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.5824±0.0482</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4872±0.0104</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.4996±0.0327</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5407±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5689±0.0512</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5689±0.0512</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5689±0.0512</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.5004±0.0005</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.6099±0.0358</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>0.4974±0.0036</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.5040±0.0034</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4795±0.0175</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5458±0.0512</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.5692±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4714±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4703±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.5659±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.6549±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.6549±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.6549±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.5879±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6165±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.6593±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.4374±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.4374±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4736±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4440±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4996±0.0005</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5022±0.0000</t>
+          <t>0.5117±0.0019</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5308±0.0000</t>
+          <t>0.5293±0.0163</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5308±0.0000</t>
+          <t>0.5293±0.0163</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5308±0.0000</t>
+          <t>0.5293±0.0163</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5033±0.0000</t>
+          <t>0.5260±0.0360</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5626±0.0000</t>
+          <t>0.5480±0.0359</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5220±0.0000</t>
+          <t>0.5289±0.0109</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0000±0.0000</t>
+          <t>0.1546±0.2186</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1365,447 +1365,447 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>0.6497±0.0037</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6386±0.0203</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6199±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6899±0.0119</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6899±0.0119</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6899±0.0119</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.6742±0.0106</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6380±0.0068</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6966±0.0194</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.6248±0.0593</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.7086±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.7086±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.7086±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6279±0.0151</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6318±0.0219</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6628±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.7377±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7000±0.0338</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6884±0.0304</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6884±0.0304</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6884±0.0304</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.7053±0.0114</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.6982±0.0207</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6548±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6578±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.3199±0.2452</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6110±0.0065</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6543±0.0118</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.6639±0.0040</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.6676±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.6676±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6676±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6861±0.0231</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6861±0.0231</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6861±0.0231</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7307±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6937±0.0112</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6946±0.0191</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.2988±0.2618</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.7068±0.0074</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6303±0.0077</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6325±0.0223</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6675±0.0012</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7250±0.0107</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7314±0.0077</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7314±0.0077</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7314±0.0077</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7351±0.0171</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7376±0.0038</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7382±0.0091</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6342±0.0234</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6234±0.0310</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6386±0.0171</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.5789±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6652±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0153</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0153</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6771±0.0153</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.6629±0.0044</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6906±0.0221</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.2222±0.3143</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6502±0.0104</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6384±0.0064</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6838±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6889±0.0238</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6889±0.0238</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6889±0.0238</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.6933±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6320±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6321±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6667±0.0004</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.7043±0.0099</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0.6644±0.0032</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6685±0.0015</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6352±0.0209</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6520±0.0345</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.6931±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7191±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7191±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7191±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7021±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7079±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7237±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.5789±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.5789±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6341±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.5886±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.6667±0.0000</t>
+          <t>0.6663±0.0005</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6676±0.0000</t>
+          <t>0.6719±0.0008</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6797±0.0074</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6797±0.0074</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.6797±0.0074</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6681±0.0000</t>
+          <t>0.6787±0.0167</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6938±0.0000</t>
+          <t>0.6876±0.0152</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6756±0.0000</t>
+          <t>0.6797±0.0048</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.5853±0.0000</t>
+          <t>0.5012±0.0622</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6706±0.0000</t>
+          <t>0.6515±0.0113</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.5152±0.0000</t>
+          <t>0.5873±0.0049</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5853±0.0000</t>
+          <t>0.6029±0.0164</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6614±0.0000</t>
+          <t>0.6583±0.0098</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7333±0.0000</t>
+          <t>0.6834±0.0203</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6852±0.0000</t>
+          <t>0.6274±0.0157</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.7368±0.0000</t>
+          <t>0.7227±0.0312</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7368±0.0000</t>
+          <t>0.7227±0.0312</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.7368±0.0000</t>
+          <t>0.7227±0.0312</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6717±0.0000</t>
+          <t>0.6562±0.0402</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6690±0.0000</t>
+          <t>0.6518±0.0051</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.7554±0.0000</t>
+          <t>0.7473±0.0158</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5916±0.0000</t>
+          <t>0.5819±0.0376</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.6956±0.0000</t>
+          <t>0.7014±0.0255</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4618±0.0000</t>
+          <t>0.6638±0.0133</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.6004±0.0000</t>
+          <t>0.6707±0.0073</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6524±0.0000</t>
+          <t>0.6554±0.0137</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6440±0.0000</t>
+          <t>0.6510±0.0130</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7536±0.0000</t>
+          <t>0.7688±0.0045</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7828±0.0000</t>
+          <t>0.7878±0.0082</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7828±0.0000</t>
+          <t>0.7878±0.0082</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7828±0.0000</t>
+          <t>0.7878±0.0082</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7674±0.0175</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.7852±0.0000</t>
+          <t>0.7635±0.0204</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7799±0.0000</t>
+          <t>0.7887±0.0048</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.5849±0.0000</t>
+          <t>0.5186±0.0677</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6152±0.0000</t>
+          <t>0.6092±0.0158</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.5892±0.0000</t>
+          <t>0.5928±0.0066</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.5861±0.0000</t>
+          <t>0.6606±0.0239</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6493±0.0000</t>
+          <t>0.6547±0.0101</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.6554±0.0135</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.5734±0.0000</t>
+          <t>0.5474±0.0242</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5719±0.0000</t>
+          <t>0.7062±0.0394</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5719±0.0000</t>
+          <t>0.7062±0.0394</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.5719±0.0000</t>
+          <t>0.7062±0.0394</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.5613±0.0000</t>
+          <t>0.5458±0.0313</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.8420±0.0000</t>
+          <t>0.8170±0.0216</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5731±0.0000</t>
+          <t>0.7053±0.0317</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.5840±0.0000</t>
+          <t>0.5137±0.0636</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.6885±0.0000</t>
+          <t>0.7348±0.0219</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4353±0.0000</t>
+          <t>0.6121±0.0107</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4462±0.0000</t>
+          <t>0.6377±0.0182</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.6479±0.0000</t>
+          <t>0.7201±0.0137</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5232±0.0000</t>
+          <t>0.6745±0.0217</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.6693±0.0000</t>
+          <t>0.7581±0.0120</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7786±0.0062</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7786±0.0062</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.7456±0.0000</t>
+          <t>0.7786±0.0062</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.6820±0.0000</t>
+          <t>0.7854±0.0190</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.7274±0.0000</t>
+          <t>0.7995±0.0113</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.7413±0.0000</t>
+          <t>0.7714±0.0031</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6059±0.0000</t>
+          <t>0.6033±0.0286</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6284±0.0000</t>
+          <t>0.6320±0.0141</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.5783±0.0000</t>
+          <t>0.5875±0.0036</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.5899±0.0000</t>
+          <t>0.6363±0.0379</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6548±0.0000</t>
+          <t>0.6545±0.0111</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6517±0.0000</t>
+          <t>0.6565±0.0132</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6351±0.0000</t>
+          <t>0.6272±0.0176</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6280±0.0000</t>
+          <t>0.6923±0.0328</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6280±0.0000</t>
+          <t>0.6923±0.0328</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6280±0.0000</t>
+          <t>0.6923±0.0328</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6337±0.0000</t>
+          <t>0.6301±0.0229</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.5018±0.0000</t>
+          <t>0.5215±0.0189</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6036±0.0000</t>
+          <t>0.6972±0.0367</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.5472±0.0833</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6396±0.0000</t>
+          <t>0.6341±0.0085</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.5789±0.0000</t>
+          <t>0.5895±0.0029</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.5880±0.0000</t>
+          <t>0.6390±0.0292</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6545±0.0000</t>
+          <t>0.6550±0.0102</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6591±0.0000</t>
+          <t>0.6581±0.0125</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6666±0.0000</t>
+          <t>0.6449±0.0206</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.7180±0.0269</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.7180±0.0269</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.6606±0.0000</t>
+          <t>0.7180±0.0269</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.6575±0.0000</t>
+          <t>0.6371±0.0174</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6808±0.0000</t>
+          <t>0.7135±0.0157</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6413±0.0000</t>
+          <t>0.7201±0.0314</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.5204±0.0000</t>
+          <t>0.4927±0.0370</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7280±0.0000</t>
+          <t>0.7824±0.0058</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4698±0.0000</t>
+          <t>0.6275±0.0610</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4848±0.0000</t>
+          <t>0.6848±0.0205</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6322±0.0000</t>
+          <t>0.6511±0.0098</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5830±0.0000</t>
+          <t>0.6398±0.0058</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7532±0.0000</t>
+          <t>0.7871±0.0069</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.6773±0.0000</t>
+          <t>0.7193±0.0127</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.6773±0.0000</t>
+          <t>0.7193±0.0127</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.6773±0.0000</t>
+          <t>0.7193±0.0127</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7444±0.0000</t>
+          <t>0.7530±0.0253</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.8144±0.0000</t>
+          <t>0.8185±0.0134</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.6434±0.0000</t>
+          <t>0.7123±0.0045</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6439±0.0000</t>
+          <t>0.5827±0.0368</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7021±0.0000</t>
+          <t>0.6823±0.0072</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5299±0.0000</t>
+          <t>0.6680±0.0116</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.6604±0.0000</t>
+          <t>0.6863±0.0122</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.6535±0.0000</t>
+          <t>0.6833±0.0151</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7159±0.0000</t>
+          <t>0.7077±0.0260</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7152±0.0000</t>
+          <t>0.6628±0.0139</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6915±0.0000</t>
+          <t>0.7338±0.0155</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6915±0.0000</t>
+          <t>0.7338±0.0155</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6915±0.0000</t>
+          <t>0.7338±0.0155</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7064±0.0000</t>
+          <t>0.6787±0.0285</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.7056±0.0000</t>
+          <t>0.7024±0.0035</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.7117±0.0000</t>
+          <t>0.7016±0.0228</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6224±0.0000</t>
+          <t>0.6452±0.0276</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.6990±0.0000</t>
+          <t>0.7108±0.0192</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.4807±0.0000</t>
+          <t>0.7081±0.0096</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5681±0.0000</t>
+          <t>0.7214±0.0243</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.6363±0.0000</t>
+          <t>0.6816±0.0211</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6595±0.0000</t>
+          <t>0.6786±0.0184</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7324±0.0000</t>
+          <t>0.7727±0.0018</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7902±0.0051</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7902±0.0051</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7902±0.0051</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7317±0.0000</t>
+          <t>0.7614±0.0209</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7627±0.0000</t>
+          <t>0.7392±0.0239</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7769±0.0000</t>
+          <t>0.7787±0.0098</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6366±0.0000</t>
+          <t>0.5773±0.0519</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6317±0.0000</t>
+          <t>0.6450±0.0206</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.6716±0.0000</t>
+          <t>0.6797±0.0106</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6759±0.0000</t>
+          <t>0.7293±0.0192</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6392±0.0000</t>
+          <t>0.6797±0.0165</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6585±0.0000</t>
+          <t>0.6769±0.0154</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6017±0.0000</t>
+          <t>0.5972±0.0262</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.5958±0.0000</t>
+          <t>0.7131±0.0247</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.5958±0.0000</t>
+          <t>0.7131±0.0247</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.5958±0.0000</t>
+          <t>0.7131±0.0247</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.5898±0.0000</t>
+          <t>0.5967±0.0309</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.8546±0.0000</t>
+          <t>0.8287±0.0205</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.5932±0.0000</t>
+          <t>0.6933±0.0399</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.6560±0.0000</t>
+          <t>0.5884±0.0625</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.6701±0.0000</t>
+          <t>0.7194±0.0353</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4666±0.0000</t>
+          <t>0.6862±0.0046</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4725±0.0000</t>
+          <t>0.6923±0.0243</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6316±0.0000</t>
+          <t>0.7293±0.0163</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.5122±0.0000</t>
+          <t>0.7025±0.0254</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.6537±0.0000</t>
+          <t>0.7514±0.0194</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.7131±0.0000</t>
+          <t>0.7702±0.0090</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.7131±0.0000</t>
+          <t>0.7702±0.0090</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.7131±0.0000</t>
+          <t>0.7702±0.0090</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.6511±0.0000</t>
+          <t>0.7816±0.0138</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.6946±0.0000</t>
+          <t>0.7943±0.0206</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.6938±0.0000</t>
+          <t>0.7584±0.0059</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6613±0.0000</t>
+          <t>0.6634±0.0196</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6291±0.0000</t>
+          <t>0.6560±0.0157</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.6715±0.0000</t>
+          <t>0.6753±0.0044</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.6761±0.0000</t>
+          <t>0.7096±0.0209</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6457±0.0000</t>
+          <t>0.6787±0.0176</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6425±0.0000</t>
+          <t>0.6814±0.0201</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.6406±0.0000</t>
+          <t>0.6592±0.0206</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6389±0.0000</t>
+          <t>0.7026±0.0228</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6389±0.0000</t>
+          <t>0.7026±0.0228</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6389±0.0000</t>
+          <t>0.7026±0.0228</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6406±0.0000</t>
+          <t>0.6616±0.0245</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.6107±0.0000</t>
+          <t>0.6006±0.0331</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6328±0.0000</t>
+          <t>0.6870±0.0471</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6449±0.0000</t>
+          <t>0.6115±0.0578</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6045±0.0000</t>
+          <t>0.6326±0.0152</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.6699±0.0000</t>
+          <t>0.6813±0.0102</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6685±0.0000</t>
+          <t>0.7132±0.0154</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.6470±0.0000</t>
+          <t>0.6792±0.0174</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.6493±0.0000</t>
+          <t>0.6810±0.0206</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6620±0.0000</t>
+          <t>0.6733±0.0213</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6604±0.0000</t>
+          <t>0.7220±0.0184</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6604±0.0000</t>
+          <t>0.7220±0.0184</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6604±0.0000</t>
+          <t>0.7220±0.0184</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.6563±0.0000</t>
+          <t>0.6655±0.0175</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.7610±0.0000</t>
+          <t>0.7705±0.0136</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6589±0.0000</t>
+          <t>0.6940±0.0435</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.5693±0.0350</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7034±0.0000</t>
+          <t>0.7798±0.0098</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4847±0.0000</t>
+          <t>0.6510±0.0885</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.4960±0.0000</t>
+          <t>0.6832±0.0234</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6263±0.0000</t>
+          <t>0.6745±0.0160</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6039±0.0000</t>
+          <t>0.6656±0.0155</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7254±0.0000</t>
+          <t>0.7799±0.0138</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.6162±0.0000</t>
+          <t>0.6787±0.0064</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.6162±0.0000</t>
+          <t>0.6787±0.0064</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.6162±0.0000</t>
+          <t>0.6787±0.0064</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7150±0.0000</t>
+          <t>0.7438±0.0183</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7972±0.0000</t>
+          <t>0.8021±0.0178</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.5863±0.0000</t>
+          <t>0.6696±0.0165</t>
         </is>
       </c>
     </row>
